--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_p99_heatmap_1Mbps.xlsx
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>15778</v>
+        <v>17508</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>13082</v>
+        <v>15068</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5592</v>
+        <v>10728</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>15778</v>
+        <v>17508</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>13318</v>
+        <v>13642</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6198</v>
+        <v>9962</v>
       </c>
     </row>
     <row r="6">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>17138</v>
+        <v>18852</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>14908</v>
+        <v>15402</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>14778</v>
+        <v>17932</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17538</v>
+        <v>18278</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16318</v>
+        <v>19722</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>15182</v>
+        <v>17412</v>
       </c>
     </row>
     <row r="7">
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>19592</v>
+        <v>21182</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>19128</v>
+        <v>19828</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18052</v>
+        <v>17438</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>19242</v>
+        <v>18718</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>19278</v>
+        <v>21792</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>17652</v>
+        <v>23378</v>
       </c>
     </row>
     <row r="8">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>16712</v>
+        <v>22292</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>19738</v>
+        <v>22818</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>22898</v>
+        <v>23758</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>17592</v>
+        <v>21038</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>19512</v>
+        <v>23982</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>20638</v>
+        <v>23182</v>
       </c>
     </row>
     <row r="9">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18728</v>
+        <v>20392</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>20268</v>
+        <v>21258</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>23318</v>
+        <v>22458</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>18898</v>
+        <v>21058</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>20162</v>
+        <v>23438</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>20138</v>
+        <v>21648</v>
       </c>
     </row>
     <row r="10">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>19282</v>
+        <v>20122</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18762</v>
+        <v>23198</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>21752</v>
+        <v>22888</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>19598</v>
+        <v>21172</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>18548</v>
+        <v>23232</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>19722</v>
+        <v>22072</v>
       </c>
     </row>
     <row r="12">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>16922</v>
+        <v>18128</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>14182</v>
+        <v>16162</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12278</v>
+        <v>15132</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16922</v>
+        <v>18128</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>14412</v>
+        <v>15878</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11352</v>
+        <v>13108</v>
       </c>
     </row>
     <row r="15">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>18788</v>
+        <v>20942</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>17592</v>
+        <v>19918</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>19292</v>
+        <v>21548</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>18632</v>
+        <v>22422</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>16898</v>
+        <v>20498</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>18602</v>
+        <v>21068</v>
       </c>
     </row>
     <row r="16">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>20248</v>
+        <v>22352</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21832</v>
+        <v>25628</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>21972</v>
+        <v>24892</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>20128</v>
+        <v>22558</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>20768</v>
+        <v>25212</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>22632</v>
+        <v>25622</v>
       </c>
     </row>
     <row r="17">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>19968</v>
+        <v>21398</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>21668</v>
+        <v>25088</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>22598</v>
+        <v>25528</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>19708</v>
+        <v>22352</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>21048</v>
+        <v>25662</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>25172</v>
+        <v>24908</v>
       </c>
     </row>
     <row r="18">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>20072</v>
+        <v>22688</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>22768</v>
+        <v>25392</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>22692</v>
+        <v>28402</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>20092</v>
+        <v>22862</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>23312</v>
+        <v>25822</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>24422</v>
+        <v>28762</v>
       </c>
     </row>
     <row r="19">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>20272</v>
+        <v>22872</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>21518</v>
+        <v>24912</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>23998</v>
+        <v>25362</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>21518</v>
+        <v>22798</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>22682</v>
+        <v>24488</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>24872</v>
+        <v>25598</v>
       </c>
     </row>
     <row r="21">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>18408</v>
+        <v>19872</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>16828</v>
+        <v>18838</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10492</v>
+        <v>11132</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G23" s="6" t="n">
-        <v>18408</v>
+        <v>19872</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>16288</v>
+        <v>18328</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9482</v>
+        <v>12258</v>
       </c>
     </row>
     <row r="24">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>20208</v>
+        <v>23652</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>23692</v>
+        <v>26092</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>13968</v>
+        <v>14178</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>21352</v>
+        <v>24558</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>21778</v>
+        <v>27188</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>15792</v>
+        <v>20632</v>
       </c>
     </row>
     <row r="25">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>21708</v>
+        <v>25322</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>26162</v>
+        <v>27988</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>28668</v>
+        <v>32352</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>22218</v>
+        <v>24128</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>25492</v>
+        <v>28898</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>25818</v>
+        <v>33372</v>
       </c>
     </row>
     <row r="26">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>22548</v>
+        <v>25318</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>25828</v>
+        <v>28872</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>28952</v>
+        <v>31732</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>21602</v>
+        <v>24188</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>26178</v>
+        <v>29158</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>29432</v>
+        <v>30972</v>
       </c>
     </row>
     <row r="27">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>21882</v>
+        <v>24182</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>26248</v>
+        <v>28612</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>29382</v>
+        <v>31752</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>21802</v>
+        <v>24118</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>24478</v>
+        <v>27522</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>25612</v>
+        <v>30352</v>
       </c>
     </row>
     <row r="28">
@@ -1751,13 +1751,13 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>20322</v>
+        <v>22498</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>23368</v>
+        <v>26122</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>27278</v>
+        <v>26608</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>20998</v>
+        <v>22078</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>23332</v>
+        <v>27628</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>28478</v>
+        <v>28762</v>
       </c>
     </row>
   </sheetData>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>17652</v>
+        <v>20258</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>19128</v>
+        <v>21158</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>16978</v>
+        <v>21172</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>17652</v>
+        <v>20258</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18678</v>
+        <v>20538</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>17168</v>
+        <v>20842</v>
       </c>
     </row>
     <row r="6">
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>18672</v>
+        <v>20922</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18372</v>
+        <v>20038</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>18102</v>
+        <v>20832</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>18162</v>
+        <v>20648</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>18508</v>
+        <v>20512</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>18028</v>
+        <v>20848</v>
       </c>
     </row>
     <row r="7">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>18208</v>
+        <v>20672</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>18918</v>
+        <v>20272</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17732</v>
+        <v>19628</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>18042</v>
+        <v>19772</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18328</v>
+        <v>21018</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>17812</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="8">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>18348</v>
+        <v>20292</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>18128</v>
+        <v>19918</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>17818</v>
+        <v>19548</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>18322</v>
+        <v>19652</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>17848</v>
+        <v>20078</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>17698</v>
+        <v>20228</v>
       </c>
     </row>
     <row r="9">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18158</v>
+        <v>19672</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>18048</v>
+        <v>19718</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>18428</v>
+        <v>19858</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>17968</v>
+        <v>20438</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18558</v>
+        <v>20642</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>17838</v>
+        <v>19522</v>
       </c>
     </row>
     <row r="10">
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>18192</v>
+        <v>19922</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>17532</v>
+        <v>20608</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>18278</v>
+        <v>20502</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>17662</v>
+        <v>20922</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>17868</v>
+        <v>21258</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>17658</v>
+        <v>19952</v>
       </c>
     </row>
     <row r="12">
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>18098</v>
+        <v>19978</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>18712</v>
+        <v>21418</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18558</v>
+        <v>21852</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>18098</v>
+        <v>19978</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>18922</v>
+        <v>21022</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>18008</v>
+        <v>21128</v>
       </c>
     </row>
     <row r="15">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>18528</v>
+        <v>20462</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>18302</v>
+        <v>20942</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>18188</v>
+        <v>21002</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>18728</v>
+        <v>21588</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>18392</v>
+        <v>21738</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>18192</v>
+        <v>21418</v>
       </c>
     </row>
     <row r="16">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>18958</v>
+        <v>20228</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18708</v>
+        <v>22468</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>18682</v>
+        <v>21078</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>19232</v>
+        <v>20712</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>18078</v>
+        <v>21342</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>19082</v>
+        <v>21248</v>
       </c>
     </row>
     <row r="17">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>18722</v>
+        <v>20422</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>18648</v>
+        <v>21942</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>18482</v>
+        <v>21328</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>18498</v>
+        <v>20918</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18472</v>
+        <v>21812</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>19688</v>
+        <v>20352</v>
       </c>
     </row>
     <row r="18">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>18592</v>
+        <v>21378</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>19002</v>
+        <v>21582</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17888</v>
+        <v>21822</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>18422</v>
+        <v>21082</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19398</v>
+        <v>21822</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>19088</v>
+        <v>22028</v>
       </c>
     </row>
     <row r="19">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>18418</v>
+        <v>20798</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>18078</v>
+        <v>21352</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19252</v>
+        <v>20142</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>19328</v>
+        <v>20568</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>18398</v>
+        <v>20688</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>19038</v>
+        <v>20462</v>
       </c>
     </row>
   </sheetData>

--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_p99_heatmap_1Mbps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,11 +34,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0079C0FF"/>
+      <color rgb="00E3B341"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00E3B341"/>
+      <color rgb="0079C0FF"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -106,7 +106,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -501,7 +504,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>All STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>All STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -515,475 +518,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1718</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1718</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1852</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1968</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2052</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>1968</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2042</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2068</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>10598</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>10762</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>10912</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>10598</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>10862</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>11032</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>10438</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>10532</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>10542</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>10508</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>10542</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>10672</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>10312</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>10292</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>10302</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>10368</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>10482</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>10308</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>10348</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>10348</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>10338</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>10162</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>10392</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>10402</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>10338</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>10348</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>10482</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>10498</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>10582</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>10728</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>10738</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>10458</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>10688</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>10698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>14588</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>14788</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>14948</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>14588</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>14982</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>15132</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>14312</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>14578</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>14572</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="n">
+        <v>14372</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>14508</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>14718</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n">
+        <v>14198</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>14298</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>14362</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>14248</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>14402</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>14342</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>14148</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>14168</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>14248</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="n">
+        <v>14192</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>14118</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>14278</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>14062</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>14072</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>14102</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>14032</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>14168</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>14212</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>14128</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>14298</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>14308</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
+      <c r="G29" s="7" t="n">
+        <v>14118</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>14252</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>14262</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1702</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1668</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1692</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1792</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2108</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2162</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>2112</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>2092</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2202</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>2172</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2248</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>2268</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>2348</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2212</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2212</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2322</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2078</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2228</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2292</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2332</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2278</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2462</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>11152</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>11258</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>11392</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>11152</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>11208</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>11522</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>10672</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>10902</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>10922</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>10562</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>10878</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>11182</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>10498</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>10568</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>10478</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>10468</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>10612</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>10678</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>10332</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>10368</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>10412</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>10252</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>10518</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>10438</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>10592</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>10678</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>10768</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>10388</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>10838</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>11038</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>11048</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>11228</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>11368</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>11152</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>11512</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>11598</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>15682</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>15802</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>15868</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>15682</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>15958</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>16252</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>14818</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>15128</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>15188</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>14782</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>15312</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>15748</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>14712</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>14912</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>14852</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>14732</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>15072</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>15388</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>14508</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>14572</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>14782</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>14402</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>14778</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>14892</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>14402</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>14482</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>14602</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>14232</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>14732</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>14972</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>14518</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>14728</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>14932</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>14682</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>15018</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>15238</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1652</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1652</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1702</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>2242</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>2308</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2218</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>2342</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>2382</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>2418</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>2202</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>2382</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>2542</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2408</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>2668</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2718</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>2672</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>2348</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2698</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>11338</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>11558</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>11502</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>11338</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>11522</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>11472</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>10618</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>10802</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>11052</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>10822</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>11042</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>11212</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>10118</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>10642</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>10792</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>10522</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>10618</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>10698</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>10132</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>10478</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>10072</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>10488</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>10662</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>11062</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>10772</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>11212</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>11432</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>11298</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>12032</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>12062</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>11438</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>12222</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>12748</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>16058</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>16262</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>16288</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>16058</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>16312</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>16528</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>14958</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>15268</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>15528</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>15162</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>15768</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>16088</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>14712</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>15292</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>15518</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>15042</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>15488</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>15938</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>14608</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>14832</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>15202</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>14532</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>15208</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>15582</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>14548</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>14568</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>14968</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>14612</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>15132</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>15368</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>14838</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>15682</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>15618</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>14972</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>15728</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>16442</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -995,7 +2618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1007,7 +2630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1019,7 +2642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1031,7 +2654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1043,8 +2666,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1066,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1083,7 +2850,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P-EDCA STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>P-EDCA STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1097,691 +2864,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>17508</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>15068</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>10728</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1192</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1198</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1188</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>17508</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>13642</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>9962</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1192</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1178</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>18852</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>15402</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>17932</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1478</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1502</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>18278</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>19722</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>17412</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1478</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1488</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>21182</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>19828</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>17438</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1822</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>18718</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>21792</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>23378</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>22292</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>22818</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>23758</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>21038</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>23982</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>23182</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>20392</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>21258</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>22458</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2118</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2068</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>21058</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>23438</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>21648</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2132</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>20122</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>23198</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>22888</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2122</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2272</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2288</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>21172</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>23232</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>22072</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>2068</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2232</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>18128</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>16162</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>15132</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>7778</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>6078</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>5612</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>18128</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>15878</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>13108</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>7778</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>5208</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>20942</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>19918</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>21548</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>6882</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>6132</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5882</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>22422</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>20498</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>21068</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>7532</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>5312</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>22352</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>25628</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>24892</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>7322</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>6682</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>6542</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>22558</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>25212</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>25622</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>7328</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>6592</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>6278</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>21398</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>25088</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>25528</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>8222</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>7992</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>7978</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>22352</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>25662</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>24908</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>8198</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>7842</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>22688</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>25392</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>28402</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>9268</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>9052</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>9132</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>22862</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>25822</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>28762</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>9238</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>9288</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>9272</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>22872</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>24912</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>25362</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>10308</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>10568</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>10598</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>22798</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>24488</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>25598</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>10348</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>10382</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>10528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>19872</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>18838</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>11132</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>12932</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>12162</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>11708</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>19872</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>18328</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>12258</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>12932</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>11882</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>10802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>23652</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>26092</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>14178</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>12098</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>11978</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>11602</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>24558</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>27188</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>20632</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="n">
+        <v>12628</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>11248</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>10592</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>25322</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>27988</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>32352</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n">
+        <v>12188</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>11182</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>10538</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>24128</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>28898</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>33372</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>12072</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>10932</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>8998</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>25318</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>28872</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>31732</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>12158</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>10948</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>10808</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>24188</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>29158</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>30972</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="n">
+        <v>11878</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>10228</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>24182</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>28612</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>31752</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>12368</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>11668</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>11808</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>24118</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>27522</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>30352</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>12218</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>12058</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>11918</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>22498</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>26122</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>26608</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>13422</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>13558</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>13558</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>22078</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>27628</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>28762</v>
+      <c r="G29" s="7" t="n">
+        <v>13678</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>13312</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>13442</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1408</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1412</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1442</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1408</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1412</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1582</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1678</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1602</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1678</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2072</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>2138</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2202</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>2258</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>2308</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2252</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2252</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2132</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2362</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2322</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2408</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2462</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2612</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>10018</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>9712</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>9818</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>10018</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>9302</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>9488</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>9382</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>9508</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>9548</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>9282</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>9102</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>9108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>9078</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>8532</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>8568</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>9038</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>8302</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>8068</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>9168</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>9002</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>9148</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>9038</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>9068</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>8982</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>9998</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>10122</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>9928</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>10028</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>10318</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>10938</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>11138</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>11292</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>11082</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>11362</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>11528</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>14898</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>14928</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>15042</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>14898</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>14718</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>14998</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>14198</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>14338</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>14378</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>13962</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>14328</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>14458</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>13788</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>13658</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>13782</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>13878</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>13648</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>13568</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>13402</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>13248</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>13348</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>13178</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>13052</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>12748</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>13438</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>13272</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>13322</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>13402</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>13218</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>13552</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>14222</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>14322</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>14512</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>14342</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>14552</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>14762</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1652</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1652</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1702</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>2242</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>2308</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2218</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>2342</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>2382</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>2418</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>2202</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>2382</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>2542</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2408</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>2668</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2718</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>2672</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>2348</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2698</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>11338</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>11558</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>11502</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>11338</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>11522</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>11472</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>10618</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>10802</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>11052</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>10828</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>11042</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>11212</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>10122</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>10642</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>10792</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>10522</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>10618</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>10698</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>10138</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>10478</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>10072</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>10492</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>10662</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>11062</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>10772</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>11218</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>11432</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>11298</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>12032</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>12062</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>11442</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>12222</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>12748</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>16062</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>16262</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>16288</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>16062</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>16318</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>16528</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>14962</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>15268</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>15528</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>15162</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>15772</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>16088</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>14712</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>15298</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>15522</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>15052</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>15492</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>15938</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>14608</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>14832</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>15208</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>14532</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>15212</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>15592</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>14552</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>14572</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>14978</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>14612</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>15132</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>15372</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>14848</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>15682</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>15618</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>14978</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>15732</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>16448</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1793,7 +4964,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1805,7 +4976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1817,7 +4988,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1829,7 +5000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1841,8 +5012,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1864,7 +5179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1881,7 +5196,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legacy STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>Legacy STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1895,461 +5210,1397 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>20258</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>21158</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>21172</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2232</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>20258</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>20538</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>20842</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>2232</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>20922</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>20038</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>20832</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>2078</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2088</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>20648</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>20512</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>20848</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>2042</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>20672</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>20272</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>19628</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>19772</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>21018</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>21112</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>2108</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>20292</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>19918</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>19548</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2052</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>19652</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>20078</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>20228</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>19672</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>19718</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>19858</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>20438</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>20642</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>19522</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>19922</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>20608</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>20502</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>20922</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>21258</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>19952</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2032</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>19978</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>21418</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>21852</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>10992</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>11342</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>11528</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>19978</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>21022</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>21128</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>10992</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>11438</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>11782</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>20462</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>20942</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>21002</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>10842</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>11052</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>11102</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>21588</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>21738</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>21418</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>10932</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>11118</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>11312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>20228</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>22468</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>21078</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>10752</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>10832</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>10922</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>20712</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>21342</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>21248</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>10828</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>11002</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>10968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>20422</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>21942</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>21328</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>10722</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>10842</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>10842</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>20918</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>21812</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>20352</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>10732</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>10688</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>10968</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>21378</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>21582</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>21822</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>10688</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>10662</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>10682</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>21082</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>21822</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>22028</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>10612</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>10822</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>10852</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>20798</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>21352</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>20142</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>10668</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>10808</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>10788</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>20568</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>20688</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>20462</v>
+      <c r="G20" s="7" t="n">
+        <v>10498</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>10782</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>10772</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>14848</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>15112</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>15362</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>14848</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>15352</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>15592</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>14592</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>14908</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>14958</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>14622</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>14892</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>15132</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>14498</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>14678</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>14728</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>14552</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>14748</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>14758</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>14392</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>14552</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>14618</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>14718</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>14328</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>14428</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>14478</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>14348</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>14522</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>14612</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>14308</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>14468</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>14522</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>14258</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>14468</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>14472</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>2372</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>2558</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>2642</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2372</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>2622</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>2282</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2482</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2242</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2442</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2232</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>2302</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>2242</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2412</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>2222</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2312</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>2302</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2222</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>2418</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2188</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2288</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2368</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2158</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2202</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2318</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>12192</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>12462</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>12592</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>12192</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>12732</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>13118</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>11582</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>12048</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>12042</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>11542</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>12122</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>12718</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>11588</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>11932</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>11758</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>11532</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>12122</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>12492</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>11362</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>11672</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>11778</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>11398</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>12192</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>11318</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>11518</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>11672</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>11048</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>11898</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>12128</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>11228</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>11402</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>11508</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>11258</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>11778</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>11732</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>16252</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>16632</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>16608</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>16252</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>16938</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>17268</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>15338</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>15808</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>15918</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>15442</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>16212</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>16722</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>15402</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>15798</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>15718</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>15448</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>15968</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>16502</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>15308</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>15508</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>15808</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>15268</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>15922</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>16158</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>15112</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>15422</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>15532</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>14942</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>15772</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>16108</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>14888</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>15302</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>15462</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>15038</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>15578</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>15882</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2361,7 +6612,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2373,7 +6624,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2385,8 +6636,104 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:D29">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:I29">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
